--- a/astro-site/public/dl/pizza-shop-checklist-templates/04-pizza-shop-duties-by-role.xlsx
+++ b/astro-site/public/dl/pizza-shop-checklist-templates/04-pizza-shop-duties-by-role.xlsx
@@ -1275,7 +1275,7 @@
       </c>
       <c r="B21" s="34" t="inlineStr">
         <is>
-          <t>Remove oven ash when cold into a lidded METAL container, never trash or plastic (NFPA 96)</t>
+          <t>Ash: never take it out hot at close; remove it cold, usually first thing next morning before lighting, into a closed METAL container kept at least 3 ft from the oven, never trash or plastic (NFPA 96)</t>
         </is>
       </c>
       <c r="C21" s="27" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="E21" s="27" t="inlineStr">
         <is>
-          <t>11:00 PM</t>
+          <t>Next AM</t>
         </is>
       </c>
       <c r="F21" s="28" t="n"/>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E6" s="27" t="inlineStr">
         <is>
-          <t>10:00 AM</t>
+          <t>9:00 AM</t>
         </is>
       </c>
       <c r="F6" s="28" t="n"/>
@@ -2394,9 +2394,9 @@
       <c r="A20" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>Close the shop: alarm, lights, gas</t>
+      <c r="B20" s="33" t="inlineStr">
+        <is>
+          <t>Close the shop: gas off, lights off, then set the alarm</t>
         </is>
       </c>
       <c r="C20" s="27" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>Serve pizzas and drinks (beer and wine only if your license allows; 21+ with ID)</t>
+          <t>Serve pizzas and drinks (beer and wine only if your license allows; 21+ with ID; never serve anyone visibly intoxicated)</t>
         </is>
       </c>
       <c r="C13" s="27" t="inlineStr">
@@ -3488,9 +3488,9 @@
       <c r="A18" s="25" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>Report delivery issues</t>
+      <c r="B18" s="33" t="inlineStr">
+        <is>
+          <t>Report delivery issues and log your miles: drivers using their own car get reimbursed so vehicle costs never push pay below minimum wage (FLSA)</t>
         </is>
       </c>
       <c r="C18" s="27" t="inlineStr">
